--- a/files/九龙-茶果岭、油塘及鲤鱼门-柏景峰.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-柏景峰.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +44,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +144,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +219,57 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +646,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -35737,4 +35909,7131 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$742万
+$18,462/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$669万
+$17,639/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$726万
+$19,365/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$694万
+$18,749/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$788万
+$19,590/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$732万
+$19,314/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$722万
+$19,248/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$679万
+$18,358/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$686万
+$17,066/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$730万
+$19,256/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$720万
+$19,192/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$664万
+$17,933/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$833万
+$19,332/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$707万
+$16,404/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$698万
+$16,201/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$643万
+$15,989/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$612万
+$16,149/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$589万
+$15,713/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$621万
+$16,774/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$843万
+$19,566/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$705万
+$16,353/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$696万
+$16,152/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$641万
+$15,941/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$607万
+$16,007/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$619万
+$16,494/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$578万
+$15,622/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$841万
+$19,510/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$703万
+$16,306/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$694万
+$16,103/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$639万
+$15,894/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$622万
+$16,419/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$603万
+$16,079/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$590万
+$15,942/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$838万
+$19,450/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$742万
+$17,213/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$761万
+$17,659/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$637万
+$15,848/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$683万
+$18,016/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$625万
+$16,671/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$591万
+$15,984/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$710万
+$16,483/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$688万
+$15,968/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$728万
+$16,882/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$635万
+$15,799/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$667万
+$17,597/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$599万
+$15,971/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$576万
+$15,559/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$704万
+$16,337/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$682万
+$15,826/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$721万
+$16,732/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$628万
+$15,611/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$615万
+$16,219/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$572万
+$15,266/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$563万
+$15,222/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$704万
+$16,337/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$682万
+$15,826/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$674万
+$15,629/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$631万
+$15,689/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$635万
+$16,744/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$572万
+$15,266/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$563万
+$15,222/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$824万
+$19,107/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$678万
+$15,732/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$670万
+$15,537/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$618万
+$15,363/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$571万
+$15,076/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$569万
+$15,175/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$560万
+$15,130/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+$967万
+$16,729/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$714万
+$16,572/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$686万
+$15,919/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$678万
+$15,722/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$616万
+$15,319/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$570万
+$15,031/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$582万
+$15,521/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$601万
+$16,232/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+$1117万
+$19,330/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$818万
+$18,991/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$667万
+$15,483/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$659万
+$15,290/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$614万
+$15,272/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$570万
+$15,031/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$584万
+$15,563/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$559万
+$15,116/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$816万
+$18,933/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$685万
+$15,892/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$676万
+$15,693/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$612万
+$15,228/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$568万
+$14,982/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$558万
+$14,890/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$549万
+$14,847/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$814万
+$18,877/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$665万
+$15,428/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$657万
+$15,235/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$611万
+$15,209/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$566万
+$14,937/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$557万
+$14,844/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$548万
+$14,804/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+$951万
+$16,448/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$783万
+$18,162/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$663万
+$15,381/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$674万
+$15,636/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$610万
+$15,162/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$564万
+$14,892/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$555万
+$14,801/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$546万
+$14,760/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+$948万
+$16,398/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$809万
+$18,766/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$706万
+$16,378/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$651万
+$15,107/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$601万
+$14,941/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$563万
+$14,847/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$553万
+$14,756/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$544万
+$14,714/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$699万
+$16,227/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$675万
+$15,655/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$647万
+$15,018/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$611万
+$15,199/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$572万
+$15,103/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$547万
+$14,579/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$538万
+$14,542/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+$1075万
+$18,599/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$804万
+$18,652/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$655万
+$15,207/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$647万
+$15,018/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$594万
+$14,765/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$562万
+$14,820/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$547万
+$14,579/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$538万
+$14,542/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+$992万
+$17,158/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$719万
+$16,687/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$652万
+$15,116/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$643万
+$14,929/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$590万
+$14,674/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$551万
+$14,544/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$544万
+$14,495/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$551万
+$14,880/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+$934万
+$16,156/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$693万
+$16,084/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$695万
+$16,135/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$642万
+$14,886/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$588万
+$14,632/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$550万
+$14,499/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$542万
+$14,452/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$533万
+$14,411/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+$1128万
+$19,521/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$731万
+$16,957/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$648万
+$15,026/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$640万
+$14,839/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$586万
+$14,587/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$548万
+$14,457/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$556万
+$14,831/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$532万
+$14,369/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+$985万
+$17,038/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$790万
+$18,323/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$689万
+$15,989/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$636万
+$14,750/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$585万
+$14,545/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$562万
+$14,836/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$539万
+$14,364/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I31" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$567万
+$15,337/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+$914万
+$15,806/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$659万
+$15,298/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$642万
+$14,892/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$634万
+$14,706/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$583万
+$14,501/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$545万
+$14,372/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$537万
+$14,321/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I32" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$528万
+$14,282/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+$911万
+$15,759/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$657万
+$15,251/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$659万
+$15,285/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$632万
+$14,663/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$581万
+$14,458/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$543万
+$14,329/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H33" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$535万
+$14,278/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I33" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$527万
+$14,239/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+$1110万
+$19,211/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$674万
+$15,638/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$656万
+$15,222/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$629万
+$14,604/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$579万
+$14,414/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$547万
+$14,425/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H34" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$534万
+$14,235/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I34" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$555万
+$15,000/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+$1107万
+$19,154/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$653万
+$15,144/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$635万
+$14,744/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$628万
+$14,560/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$579万
+$14,414/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$547万
+$14,425/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H35" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$534万
+$14,235/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I35" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$513万
+$13,855/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+$1105万
+$19,116/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$740万
+$17,159/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$679万
+$15,755/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$626万
+$14,533/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$576万
+$14,329/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$565万
+$14,909/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$531万
+$14,151/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I36" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$506万
+$13,680/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 578呎 (3房)
+$1102万
+$19,061/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 431呎 (2房)
+$781万
+$18,121/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>A3 | 431呎 (2房)
+$648万
+$15,044/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>A5 | 431呎 (2房)
+$626万
+$14,515/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>A6 | 402呎 (2房)
+$574万
+$14,287/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
+        <is>
+          <t>A7 | 379呎 (2房)
+$537万
+$14,156/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>A8 | 375呎 (2房)
+$545万
+$14,523/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I37" s="22" t="inlineStr">
+        <is>
+          <t>A9 | 370呎 (2房)
+$500万
+$13,513/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>A1 | 540呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>A2 | 394呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>A3 | 393呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>A5 | 393呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t>A6 | 364呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G38" s="21" t="inlineStr">
+        <is>
+          <t>A7 | 341呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H38" s="21" t="inlineStr">
+        <is>
+          <t>A8 | 337呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I38" s="21" t="inlineStr">
+        <is>
+          <t>A9 | 333呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$786万
+$19,798/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$602万
+$20,253/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$774万
+$19,309/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$622万
+$16,768/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$713万
+$19,224/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$779万
+$19,622/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$598万
+$20,128/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$770万
+$19,195/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$708万
+$19,075/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$698万
+$18,824/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$777万
+$19,562/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$596万
+$20,067/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$767万
+$19,135/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$675万
+$18,189/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$676万
+$18,221/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$645万
+$16,253/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$594万
+$20,010/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$646万
+$16,115/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$612万
+$16,486/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$592万
+$15,967/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$658万
+$16,587/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$592万
+$19,949/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$763万
+$19,022/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$590万
+$15,890/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$591万
+$15,918/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$641万
+$16,156/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$591万
+$19,892/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$760万
+$18,965/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$611万
+$16,469/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$592万
+$15,951/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$655万
+$16,488/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$558万
+$18,771/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$758万
+$18,910/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$570万
+$15,355/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$587万
+$15,832/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$638万
+$16,062/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$495万
+$16,673/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$708万
+$17,661/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$608万
+$16,390/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$609万
+$16,417/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$632万
+$15,919/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$549万
+$18,496/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$653万
+$16,276/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$577万
+$15,561/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$565万
+$15,231/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$632万
+$15,919/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$502万
+$16,900/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$616万
+$15,372/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$581万
+$15,651/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$565万
+$15,231/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$628万
+$15,822/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$510万
+$17,173/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$613万
+$15,281/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$552万
+$14,888/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$553万
+$14,915/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$626万
+$15,775/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$456万
+$15,354/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$661万
+$16,491/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$551万
+$14,844/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$552万
+$14,869/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$624万
+$15,726/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$455万
+$15,308/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$645万
+$16,083/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$549万
+$14,798/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$550万
+$14,826/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$655万
+$16,511/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$453万
+$15,263/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$622万
+$15,501/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$547万
+$14,755/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$564万
+$15,215/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$621万
+$15,634/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$465万
+$15,664/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$600万
+$14,950/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$546万
+$14,709/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$547万
+$14,736/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$668万
+$16,832/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$466万
+$15,686/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$615万
+$15,344/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$544万
+$14,668/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$545万
+$14,693/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$608万
+$15,311/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$447万
+$15,051/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$596万
+$14,861/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$581万
+$15,656/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$543万
+$14,647/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$622万
+$15,668/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$442万
+$14,873/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$589万
+$14,685/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$536万
+$14,448/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$537万
+$14,475/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$622万
+$15,668/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$473万
+$15,923/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$589万
+$14,685/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$536万
+$14,448/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$537万
+$14,475/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$601万
+$15,129/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$439万
+$14,782/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$603万
+$15,025/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$549万
+$14,785/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$534万
+$14,388/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$599万
+$15,084/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$451万
+$15,172/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$584万
+$14,552/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$531万
+$14,319/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$532万
+$14,347/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$597万
+$15,039/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$436万
+$14,696/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$582万
+$14,509/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$530万
+$14,278/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$531万
+$14,303/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$593万
+$14,949/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$448万
+$15,081/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$580万
+$14,467/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$544万
+$14,653/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$529万
+$14,260/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$592万
+$14,902/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$447万
+$15,037/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$578万
+$14,422/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$527万
+$14,193/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$527万
+$14,216/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$590万
+$14,859/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$433万
+$14,564/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$577万
+$14,380/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$562万
+$15,149/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$526万
+$14,173/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$588万
+$14,799/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$431万
+$14,519/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$575万
+$14,338/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$523万
+$14,106/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$524万
+$14,134/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$586万
+$14,756/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$431万
+$14,519/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$575万
+$14,338/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$523万
+$14,106/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$524万
+$14,134/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$585万
+$14,726/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$429万
+$14,433/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$574万
+$14,325/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$557万
+$15,011/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$521万
+$14,047/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>B1 | 397呎 (2房)
+$584万
+$14,711/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>B2 | 297呎 (1房)
+$427万
+$14,393/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>B3 | 401呎 (2房)
+$586万
+$14,618/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>B5 | 371呎 (2房)
+$534万
+$14,391/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>B6 | 371呎 (2房)
+$556万
+$14,994/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>B1 | 360呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>B2 | 260呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>B3 | 363呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>B5 | 334呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t>B6 | 333呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$612万
+$20,475/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$604万
+$20,150/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$599万
+$20,440/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$604万
+$20,625/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$608万
+$20,351/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$601万
+$20,030/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$595万
+$20,314/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$601万
+$20,498/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$607万
+$20,288/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$599万
+$19,970/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$594万
+$20,256/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$599万
+$20,440/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$821万
+$19,045/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$605万
+$20,231/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$597万
+$19,910/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$592万
+$20,195/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$597万
+$20,379/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$848万
+$19,675/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$603万
+$20,167/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$564万
+$18,800/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$590万
+$20,133/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$595万
+$20,317/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$846万
+$19,619/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$601万
+$20,107/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$562万
+$18,744/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$588万
+$20,075/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$594万
+$20,259/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$843万
+$19,559/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$600万
+$20,050/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$549万
+$18,309/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$555万
+$18,957/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$549万
+$18,740/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+$848万
+$19,728/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$714万
+$16,576/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$491万
+$16,417/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$511万
+$17,025/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$506万
+$17,269/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$484万
+$16,515/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+$809万
+$18,811/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$706万
+$16,379/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$485万
+$16,221/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$516万
+$17,198/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$474万
+$16,171/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$467万
+$15,944/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+$838万
+$19,493/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$706万
+$16,379/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$485万
+$16,221/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$467万
+$15,578/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$474万
+$16,171/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$467万
+$15,944/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+$551万
+$20,487/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+$833万
+$19,377/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$718万
+$16,665/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$482万
+$16,124/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$465万
+$15,484/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$471万
+$16,073/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$464万
+$15,848/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+$550万
+$20,428/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+$831万
+$19,321/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$823万
+$19,097/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$527万
+$17,615/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$456万
+$15,209/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$470万
+$16,028/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$463万
+$15,799/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+$789万
+$17,727/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+$745万
+$17,337/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$821万
+$19,039/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$584万
+$19,518/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$455万
+$15,164/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$471万
+$16,072/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$499万
+$17,014/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+$743万
+$16,692/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+$702万
+$16,324/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$818万
+$18,984/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$524万
+$17,512/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$454万
+$15,119/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$460万
+$15,705/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$469万
+$16,007/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+$741万
+$16,643/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+$544万
+$20,242/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+$700万
+$16,274/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$816万
+$18,926/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$522万
+$17,458/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$452万
+$15,073/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$446万
+$15,213/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$454万
+$15,503/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+$838万
+$18,840/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+$543万
+$20,186/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+$792万
+$18,422/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$813万
+$18,870/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$486万
+$16,259/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$451万
+$15,028/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$444万
+$15,169/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$453万
+$15,459/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+$725万
+$16,299/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+$541万
+$20,123/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+$685万
+$15,938/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$679万
+$15,755/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$499万
+$16,676/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$450万
+$14,985/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$443万
+$15,120/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$456万
+$15,564/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+$717万
+$16,106/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+$535万
+$19,885/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+$677万
+$15,751/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$671万
+$15,570/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$468万
+$15,649/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$444万
+$14,804/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$442万
+$15,094/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$442万
+$15,080/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+$745万
+$16,731/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+$677万
+$15,751/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$671万
+$15,570/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$479万
+$16,018/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$444万
+$14,804/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$442万
+$15,094/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$442万
+$15,080/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J27" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+$723万
+$16,251/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+$673万
+$15,654/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$667万
+$15,477/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$476万
+$15,922/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$442万
+$14,719/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$435万
+$14,853/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$439万
+$14,987/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+$721万
+$16,202/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+$530万
+$19,710/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+$671万
+$15,608/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$665万
+$15,430/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$464万
+$15,510/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$440万
+$14,674/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$434万
+$14,810/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$438万
+$14,943/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J29" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+$719万
+$16,154/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+$521万
+$19,352/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+$716万
+$16,659/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$663万
+$15,383/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$506万
+$16,917/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$439万
+$14,628/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$433万
+$14,766/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$449万
+$15,338/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J30" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+$752万
+$16,906/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+$525万
+$19,528/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+$665万
+$15,468/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$659万
+$15,290/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$470万
+$15,730/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$438万
+$14,586/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$431万
+$14,723/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I31" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$435万
+$14,853/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J31" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+$712万
+$16,011/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+$524万
+$19,472/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+$683万
+$15,876/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$667万
+$15,474/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$522万
+$17,446/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$436万
+$14,541/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$430万
+$14,676/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I32" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$434万
+$14,810/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="J32" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+$769万
+$17,275/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+$671万
+$15,608/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$649万
+$15,049/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$457万
+$15,280/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$448万
+$14,924/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H33" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$429万
+$14,633/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I33" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$433万
+$14,766/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J33" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+$697万
+$15,661/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+$652万
+$15,163/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$646万
+$14,988/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$499万
+$16,676/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$434万
+$14,456/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H34" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$427万
+$14,589/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I34" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$431万
+$14,723/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J34" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+$695万
+$15,617/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+$521万
+$19,353/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+$650万
+$15,118/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$644万
+$14,945/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$464万
+$15,529/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$434万
+$14,456/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H35" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$427万
+$14,589/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I35" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$431万
+$14,723/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J35" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+$694万
+$15,584/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+$518万
+$19,242/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+$649万
+$15,087/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$643万
+$14,915/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$532万
+$17,789/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$431万
+$14,368/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$425万
+$14,502/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I36" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$429万
+$14,633/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J36" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>C1 | 445呎 (2房)
+$709万
+$15,936/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+$516万
+$19,182/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>C2 | 430呎 (2房)
+$782万
+$18,179/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>C3 | 431呎 (2房)
+$774万
+$17,970/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>C5 | 299呎 (1房)
+$496万
+$16,579/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$430万
+$14,325/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$436万
+$14,884/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I37" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$427万
+$14,589/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J37" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>C1 | 407呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>C10 | 269呎 (开放式)
+$514万
+$19,126/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>C2 | 392呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>C3 | 393呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t>C5 | 261呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr">
+        <is>
+          <t>C6 | 300呎 (1房)
+$445万
+$14,839/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="H38" s="22" t="inlineStr">
+        <is>
+          <t>C7 | 293呎 (1房)
+$423万
+$14,424/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I38" s="22" t="inlineStr">
+        <is>
+          <t>C8 | 293呎 (1房)
+$426万
+$14,548/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="J38" s="20" t="inlineStr">
+        <is>
+          <t>C9 | 269呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-茶果岭、油塘及鲤鱼门-柏景峰.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-柏景峰.xlsx
@@ -646,7 +646,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-茶果岭、油塘及鲤鱼门-柏景峰.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-柏景峰.xlsx
@@ -3078,14 +3078,14 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K36" s="5" t="n">
-        <v>6317940</v>
+        <v>7153070</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>16848</v>
+        <v>19075</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
@@ -3606,14 +3606,14 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K44" s="5" t="n">
-        <v>6279660</v>
+        <v>7109730</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>16746</v>
+        <v>18959</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
@@ -3668,14 +3668,14 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K45" s="5" t="n">
-        <v>6368400</v>
+        <v>7210200</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>16803</v>
+        <v>19024</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
@@ -3730,14 +3730,14 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K46" s="5" t="n">
-        <v>6851250</v>
+        <v>7756875</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>17043</v>
+        <v>19296</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
@@ -4134,14 +4134,14 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K52" s="5" t="n">
-        <v>6261390</v>
+        <v>7089045</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>16697</v>
+        <v>18904</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
@@ -4196,14 +4196,14 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K53" s="5" t="n">
-        <v>6349260</v>
+        <v>7188530</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>16753</v>
+        <v>18967</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
@@ -5476,14 +5476,14 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K73" s="5" t="n">
-        <v>7336710</v>
+        <v>8306505</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>17023</v>
+        <v>19273</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
@@ -5980,14 +5980,14 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K81" s="5" t="n">
-        <v>7315830</v>
+        <v>8282865</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>16974</v>
+        <v>19218</v>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
@@ -6484,14 +6484,14 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K89" s="5" t="n">
-        <v>7293210</v>
+        <v>8257255</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>16922</v>
+        <v>19158</v>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
@@ -8500,14 +8500,14 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K121" s="5" t="n">
-        <v>7164450</v>
+        <v>8111475</v>
       </c>
       <c r="L121" s="5" t="n">
-        <v>16623</v>
+        <v>18820</v>
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
@@ -9500,14 +9500,14 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K137" s="5" t="n">
-        <v>7120950</v>
+        <v>8062225</v>
       </c>
       <c r="L137" s="5" t="n">
-        <v>16522</v>
+        <v>18706</v>
       </c>
       <c r="M137" s="3" t="inlineStr">
         <is>
@@ -9996,14 +9996,14 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K145" s="5" t="n">
-        <v>7099200</v>
+        <v>8037600</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>16471</v>
+        <v>18649</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
@@ -10500,14 +10500,14 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K153" s="5" t="n">
-        <v>7078320</v>
+        <v>8013960</v>
       </c>
       <c r="L153" s="5" t="n">
-        <v>16423</v>
+        <v>18594</v>
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
@@ -11500,14 +11500,14 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K169" s="5" t="n">
-        <v>7036560</v>
+        <v>7966680</v>
       </c>
       <c r="L169" s="5" t="n">
-        <v>16326</v>
+        <v>18484</v>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
@@ -14050,14 +14050,14 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K210" s="5" t="n">
-        <v>9816210</v>
+        <v>11113755</v>
       </c>
       <c r="L210" s="5" t="n">
-        <v>16983</v>
+        <v>19228</v>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
@@ -14484,14 +14484,14 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K217" s="5" t="n">
-        <v>6870390</v>
+        <v>7778545</v>
       </c>
       <c r="L217" s="5" t="n">
-        <v>15941</v>
+        <v>18048</v>
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
@@ -16034,14 +16034,14 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K242" s="5" t="n">
-        <v>9660480</v>
+        <v>10937440</v>
       </c>
       <c r="L242" s="5" t="n">
-        <v>16714</v>
+        <v>18923</v>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
@@ -16530,14 +16530,14 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K250" s="5" t="n">
-        <v>9631770</v>
+        <v>10904935</v>
       </c>
       <c r="L250" s="5" t="n">
-        <v>16664</v>
+        <v>18867</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
@@ -17026,14 +17026,14 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K258" s="5" t="n">
-        <v>9612630</v>
+        <v>10883265</v>
       </c>
       <c r="L258" s="5" t="n">
-        <v>16631</v>
+        <v>18829</v>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
@@ -17460,14 +17460,14 @@
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K265" s="5" t="n">
-        <v>6794700</v>
+        <v>7692850</v>
       </c>
       <c r="L265" s="5" t="n">
-        <v>15765</v>
+        <v>17849</v>
       </c>
       <c r="M265" s="3" t="inlineStr">
         <is>
@@ -17522,14 +17522,14 @@
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K266" s="5" t="n">
-        <v>9584790</v>
+        <v>10851745</v>
       </c>
       <c r="L266" s="5" t="n">
-        <v>16583</v>
+        <v>18775</v>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
@@ -19544,14 +19544,14 @@
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K295" s="5" t="n">
-        <v>6204840</v>
+        <v>7025020</v>
       </c>
       <c r="L295" s="5" t="n">
-        <v>16725</v>
+        <v>18935</v>
       </c>
       <c r="M295" s="3" t="inlineStr">
         <is>
@@ -19668,14 +19668,14 @@
       </c>
       <c r="J297" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K297" s="5" t="n">
-        <v>6736410</v>
+        <v>7626855</v>
       </c>
       <c r="L297" s="5" t="n">
-        <v>16799</v>
+        <v>19020</v>
       </c>
       <c r="M297" s="3" t="inlineStr">
         <is>
@@ -19730,14 +19730,14 @@
       </c>
       <c r="J298" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K298" s="5" t="n">
-        <v>5233050</v>
+        <v>5924775</v>
       </c>
       <c r="L298" s="5" t="n">
-        <v>17620</v>
+        <v>19949</v>
       </c>
       <c r="M298" s="3" t="inlineStr">
         <is>
@@ -19792,14 +19792,14 @@
       </c>
       <c r="J299" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K299" s="5" t="n">
-        <v>6838200</v>
+        <v>7742100</v>
       </c>
       <c r="L299" s="5" t="n">
-        <v>17225</v>
+        <v>19502</v>
       </c>
       <c r="M299" s="3" t="inlineStr">
         <is>
@@ -19916,14 +19916,14 @@
       </c>
       <c r="J301" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K301" s="5" t="n">
-        <v>6156990</v>
+        <v>6970845</v>
       </c>
       <c r="L301" s="5" t="n">
-        <v>16596</v>
+        <v>18789</v>
       </c>
       <c r="M301" s="3" t="inlineStr">
         <is>
@@ -19978,14 +19978,14 @@
       </c>
       <c r="J302" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K302" s="5" t="n">
-        <v>6696390</v>
+        <v>7581545</v>
       </c>
       <c r="L302" s="5" t="n">
-        <v>16699</v>
+        <v>18907</v>
       </c>
       <c r="M302" s="3" t="inlineStr">
         <is>
@@ -20040,14 +20040,14 @@
       </c>
       <c r="J303" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K303" s="5" t="n">
-        <v>5200860</v>
+        <v>5888330</v>
       </c>
       <c r="L303" s="5" t="n">
-        <v>17511</v>
+        <v>19826</v>
       </c>
       <c r="M303" s="3" t="inlineStr">
         <is>
@@ -20102,14 +20102,14 @@
       </c>
       <c r="J304" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K304" s="5" t="n">
-        <v>6777300</v>
+        <v>7673150</v>
       </c>
       <c r="L304" s="5" t="n">
-        <v>17071</v>
+        <v>19328</v>
       </c>
       <c r="M304" s="3" t="inlineStr">
         <is>
@@ -20288,14 +20288,14 @@
       </c>
       <c r="J307" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K307" s="5" t="n">
-        <v>6675510</v>
+        <v>7557905</v>
       </c>
       <c r="L307" s="5" t="n">
-        <v>16647</v>
+        <v>18848</v>
       </c>
       <c r="M307" s="3" t="inlineStr">
         <is>
@@ -20350,14 +20350,14 @@
       </c>
       <c r="J308" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K308" s="5" t="n">
-        <v>5185200</v>
+        <v>5870600</v>
       </c>
       <c r="L308" s="5" t="n">
-        <v>17459</v>
+        <v>19766</v>
       </c>
       <c r="M308" s="3" t="inlineStr">
         <is>
@@ -20412,14 +20412,14 @@
       </c>
       <c r="J309" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K309" s="5" t="n">
-        <v>6756420</v>
+        <v>7649510</v>
       </c>
       <c r="L309" s="5" t="n">
-        <v>17019</v>
+        <v>19268</v>
       </c>
       <c r="M309" s="3" t="inlineStr">
         <is>
@@ -20660,14 +20660,14 @@
       </c>
       <c r="J313" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K313" s="5" t="n">
-        <v>5170410</v>
+        <v>5853855</v>
       </c>
       <c r="L313" s="5" t="n">
-        <v>17409</v>
+        <v>19710</v>
       </c>
       <c r="M313" s="3" t="inlineStr">
         <is>
@@ -20908,14 +20908,14 @@
       </c>
       <c r="J317" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K317" s="5" t="n">
-        <v>6636360</v>
+        <v>7513580</v>
       </c>
       <c r="L317" s="5" t="n">
-        <v>16550</v>
+        <v>18737</v>
       </c>
       <c r="M317" s="3" t="inlineStr">
         <is>
@@ -20970,14 +20970,14 @@
       </c>
       <c r="J318" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K318" s="5" t="n">
-        <v>5154750</v>
+        <v>5836125</v>
       </c>
       <c r="L318" s="5" t="n">
-        <v>17356</v>
+        <v>19650</v>
       </c>
       <c r="M318" s="3" t="inlineStr">
         <is>
@@ -21218,14 +21218,14 @@
       </c>
       <c r="J322" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K322" s="5" t="n">
-        <v>6616350</v>
+        <v>7490925</v>
       </c>
       <c r="L322" s="5" t="n">
-        <v>16500</v>
+        <v>18681</v>
       </c>
       <c r="M322" s="3" t="inlineStr">
         <is>
@@ -21280,14 +21280,14 @@
       </c>
       <c r="J323" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K323" s="5" t="n">
-        <v>5139960</v>
+        <v>5819380</v>
       </c>
       <c r="L323" s="5" t="n">
-        <v>17306</v>
+        <v>19594</v>
       </c>
       <c r="M323" s="3" t="inlineStr">
         <is>
@@ -21528,14 +21528,14 @@
       </c>
       <c r="J327" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K327" s="5" t="n">
-        <v>6597210</v>
+        <v>7469255</v>
       </c>
       <c r="L327" s="5" t="n">
-        <v>16452</v>
+        <v>18627</v>
       </c>
       <c r="M327" s="3" t="inlineStr">
         <is>
@@ -31474,14 +31474,14 @@
       </c>
       <c r="J482" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K482" s="5" t="n">
-        <v>5257410</v>
+        <v>5952355</v>
       </c>
       <c r="L482" s="5" t="n">
-        <v>17943</v>
+        <v>20315</v>
       </c>
       <c r="M482" s="3" t="inlineStr">
         <is>
@@ -31536,14 +31536,14 @@
       </c>
       <c r="J483" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K483" s="5" t="n">
-        <v>5210430</v>
+        <v>5899165</v>
       </c>
       <c r="L483" s="5" t="n">
-        <v>17783</v>
+        <v>20134</v>
       </c>
       <c r="M483" s="3" t="inlineStr">
         <is>
@@ -31598,14 +31598,14 @@
       </c>
       <c r="J484" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K484" s="5" t="n">
-        <v>5259150</v>
+        <v>5954325</v>
       </c>
       <c r="L484" s="5" t="n">
-        <v>17530</v>
+        <v>19848</v>
       </c>
       <c r="M484" s="3" t="inlineStr">
         <is>
@@ -31660,14 +31660,14 @@
       </c>
       <c r="J485" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K485" s="5" t="n">
-        <v>5326140</v>
+        <v>6030170</v>
       </c>
       <c r="L485" s="5" t="n">
-        <v>17813</v>
+        <v>20168</v>
       </c>
       <c r="M485" s="3" t="inlineStr">
         <is>
@@ -32072,14 +32072,14 @@
       </c>
       <c r="J491" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K491" s="5" t="n">
-        <v>5225220</v>
+        <v>5915910</v>
       </c>
       <c r="L491" s="5" t="n">
-        <v>17834</v>
+        <v>20191</v>
       </c>
       <c r="M491" s="3" t="inlineStr">
         <is>
@@ -32134,14 +32134,14 @@
       </c>
       <c r="J492" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K492" s="5" t="n">
-        <v>5178240</v>
+        <v>5862720</v>
       </c>
       <c r="L492" s="5" t="n">
-        <v>17673</v>
+        <v>20009</v>
       </c>
       <c r="M492" s="3" t="inlineStr">
         <is>
@@ -32196,14 +32196,14 @@
       </c>
       <c r="J493" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K493" s="5" t="n">
-        <v>5227830</v>
+        <v>5918865</v>
       </c>
       <c r="L493" s="5" t="n">
-        <v>17426</v>
+        <v>19730</v>
       </c>
       <c r="M493" s="3" t="inlineStr">
         <is>
@@ -32258,14 +32258,14 @@
       </c>
       <c r="J494" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K494" s="5" t="n">
-        <v>5293950</v>
+        <v>5993725</v>
       </c>
       <c r="L494" s="5" t="n">
-        <v>17706</v>
+        <v>20046</v>
       </c>
       <c r="M494" s="3" t="inlineStr">
         <is>
@@ -32670,14 +32670,14 @@
       </c>
       <c r="J500" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K500" s="5" t="n">
-        <v>5210430</v>
+        <v>5899165</v>
       </c>
       <c r="L500" s="5" t="n">
-        <v>17783</v>
+        <v>20134</v>
       </c>
       <c r="M500" s="3" t="inlineStr">
         <is>
@@ -32732,14 +32732,14 @@
       </c>
       <c r="J501" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K501" s="5" t="n">
-        <v>5163450</v>
+        <v>5845975</v>
       </c>
       <c r="L501" s="5" t="n">
-        <v>17623</v>
+        <v>19952</v>
       </c>
       <c r="M501" s="3" t="inlineStr">
         <is>
@@ -32794,14 +32794,14 @@
       </c>
       <c r="J502" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K502" s="5" t="n">
-        <v>5212170</v>
+        <v>5901135</v>
       </c>
       <c r="L502" s="5" t="n">
-        <v>17374</v>
+        <v>19670</v>
       </c>
       <c r="M502" s="3" t="inlineStr">
         <is>
@@ -32856,14 +32856,14 @@
       </c>
       <c r="J503" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K503" s="5" t="n">
-        <v>5277420</v>
+        <v>5975010</v>
       </c>
       <c r="L503" s="5" t="n">
-        <v>17650</v>
+        <v>19983</v>
       </c>
       <c r="M503" s="3" t="inlineStr">
         <is>
@@ -33268,14 +33268,14 @@
       </c>
       <c r="J509" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K509" s="5" t="n">
-        <v>5194770</v>
+        <v>5881435</v>
       </c>
       <c r="L509" s="5" t="n">
-        <v>17730</v>
+        <v>20073</v>
       </c>
       <c r="M509" s="3" t="inlineStr">
         <is>
@@ -33330,14 +33330,14 @@
       </c>
       <c r="J510" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K510" s="5" t="n">
-        <v>5147790</v>
+        <v>5828245</v>
       </c>
       <c r="L510" s="5" t="n">
-        <v>17569</v>
+        <v>19892</v>
       </c>
       <c r="M510" s="3" t="inlineStr">
         <is>
@@ -33392,14 +33392,14 @@
       </c>
       <c r="J511" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K511" s="5" t="n">
-        <v>5196510</v>
+        <v>5883405</v>
       </c>
       <c r="L511" s="5" t="n">
-        <v>17322</v>
+        <v>19611</v>
       </c>
       <c r="M511" s="3" t="inlineStr">
         <is>
@@ -33454,14 +33454,14 @@
       </c>
       <c r="J512" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K512" s="5" t="n">
-        <v>5262630</v>
+        <v>5958265</v>
       </c>
       <c r="L512" s="5" t="n">
-        <v>17601</v>
+        <v>19927</v>
       </c>
       <c r="M512" s="3" t="inlineStr">
         <is>
@@ -33858,14 +33858,14 @@
       </c>
       <c r="J518" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K518" s="5" t="n">
-        <v>5179110</v>
+        <v>5863705</v>
       </c>
       <c r="L518" s="5" t="n">
-        <v>17676</v>
+        <v>20013</v>
       </c>
       <c r="M518" s="3" t="inlineStr">
         <is>
@@ -33920,14 +33920,14 @@
       </c>
       <c r="J519" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K519" s="5" t="n">
-        <v>5132130</v>
+        <v>5810515</v>
       </c>
       <c r="L519" s="5" t="n">
-        <v>17516</v>
+        <v>19831</v>
       </c>
       <c r="M519" s="3" t="inlineStr">
         <is>
@@ -34044,14 +34044,14 @@
       </c>
       <c r="J521" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K521" s="5" t="n">
-        <v>5246100</v>
+        <v>5939550</v>
       </c>
       <c r="L521" s="5" t="n">
-        <v>17545</v>
+        <v>19865</v>
       </c>
       <c r="M521" s="3" t="inlineStr">
         <is>
@@ -34106,14 +34106,14 @@
       </c>
       <c r="J522" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K522" s="5" t="n">
-        <v>7377600</v>
+        <v>8352800</v>
       </c>
       <c r="L522" s="5" t="n">
-        <v>17117</v>
+        <v>19380</v>
       </c>
       <c r="M522" s="3" t="inlineStr">
         <is>
@@ -34448,14 +34448,14 @@
       </c>
       <c r="J527" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K527" s="5" t="n">
-        <v>5164320</v>
+        <v>5846960</v>
       </c>
       <c r="L527" s="5" t="n">
-        <v>17626</v>
+        <v>19955</v>
       </c>
       <c r="M527" s="3" t="inlineStr">
         <is>
@@ -34510,14 +34510,14 @@
       </c>
       <c r="J528" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K528" s="5" t="n">
-        <v>5117340</v>
+        <v>5793770</v>
       </c>
       <c r="L528" s="5" t="n">
-        <v>17465</v>
+        <v>19774</v>
       </c>
       <c r="M528" s="3" t="inlineStr">
         <is>
@@ -34634,14 +34634,14 @@
       </c>
       <c r="J530" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K530" s="5" t="n">
-        <v>5230440</v>
+        <v>5921820</v>
       </c>
       <c r="L530" s="5" t="n">
-        <v>17493</v>
+        <v>19805</v>
       </c>
       <c r="M530" s="3" t="inlineStr">
         <is>
@@ -34696,14 +34696,14 @@
       </c>
       <c r="J531" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K531" s="5" t="n">
-        <v>7356720</v>
+        <v>8329160</v>
       </c>
       <c r="L531" s="5" t="n">
-        <v>17069</v>
+        <v>19325</v>
       </c>
       <c r="M531" s="3" t="inlineStr">
         <is>
@@ -35224,14 +35224,14 @@
       </c>
       <c r="J539" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K539" s="5" t="n">
-        <v>5215650</v>
+        <v>5905075</v>
       </c>
       <c r="L539" s="5" t="n">
-        <v>17444</v>
+        <v>19749</v>
       </c>
       <c r="M539" s="3" t="inlineStr">
         <is>
@@ -35286,14 +35286,14 @@
       </c>
       <c r="J540" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K540" s="5" t="n">
-        <v>7334100</v>
+        <v>8303550</v>
       </c>
       <c r="L540" s="5" t="n">
-        <v>17016</v>
+        <v>19266</v>
       </c>
       <c r="M540" s="3" t="inlineStr">
         <is>
@@ -35938,14 +35938,14 @@
       </c>
       <c r="J550" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K550" s="5" t="n">
-        <v>7380210</v>
+        <v>8355755</v>
       </c>
       <c r="L550" s="5" t="n">
-        <v>17163</v>
+        <v>19432</v>
       </c>
       <c r="M550" s="3" t="inlineStr">
         <is>
@@ -37102,14 +37102,14 @@
       </c>
       <c r="J568" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K568" s="5" t="n">
-        <v>7292340</v>
+        <v>8256270</v>
       </c>
       <c r="L568" s="5" t="n">
-        <v>16959</v>
+        <v>19201</v>
       </c>
       <c r="M568" s="3" t="inlineStr">
         <is>
@@ -37684,14 +37684,14 @@
       </c>
       <c r="J577" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K577" s="5" t="n">
-        <v>7248840</v>
+        <v>8207020</v>
       </c>
       <c r="L577" s="5" t="n">
-        <v>16858</v>
+        <v>19086</v>
       </c>
       <c r="M577" s="3" t="inlineStr">
         <is>
@@ -37746,14 +37746,14 @@
       </c>
       <c r="J578" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K578" s="5" t="n">
-        <v>4794570</v>
+        <v>5428335</v>
       </c>
       <c r="L578" s="5" t="n">
-        <v>17824</v>
+        <v>20180</v>
       </c>
       <c r="M578" s="3" t="inlineStr">
         <is>
@@ -38196,14 +38196,14 @@
       </c>
       <c r="J585" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K585" s="5" t="n">
-        <v>7160970</v>
+        <v>8107535</v>
       </c>
       <c r="L585" s="5" t="n">
-        <v>16615</v>
+        <v>18811</v>
       </c>
       <c r="M585" s="3" t="inlineStr">
         <is>
@@ -38258,14 +38258,14 @@
       </c>
       <c r="J586" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K586" s="5" t="n">
-        <v>7227960</v>
+        <v>8183380</v>
       </c>
       <c r="L586" s="5" t="n">
-        <v>16809</v>
+        <v>19031</v>
       </c>
       <c r="M586" s="3" t="inlineStr">
         <is>
@@ -38320,14 +38320,14 @@
       </c>
       <c r="J587" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K587" s="5" t="n">
-        <v>4780650</v>
+        <v>5412575</v>
       </c>
       <c r="L587" s="5" t="n">
-        <v>17772</v>
+        <v>20121</v>
       </c>
       <c r="M587" s="3" t="inlineStr">
         <is>
@@ -38770,14 +38770,14 @@
       </c>
       <c r="J594" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K594" s="5" t="n">
-        <v>7139220</v>
+        <v>8082910</v>
       </c>
       <c r="L594" s="5" t="n">
-        <v>16564</v>
+        <v>18754</v>
       </c>
       <c r="M594" s="3" t="inlineStr">
         <is>
@@ -39344,14 +39344,14 @@
       </c>
       <c r="J603" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K603" s="5" t="n">
-        <v>7118340</v>
+        <v>8059270</v>
       </c>
       <c r="L603" s="5" t="n">
-        <v>16516</v>
+        <v>18699</v>
       </c>
       <c r="M603" s="3" t="inlineStr">
         <is>
@@ -39918,14 +39918,14 @@
       </c>
       <c r="J612" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K612" s="5" t="n">
-        <v>7096590</v>
+        <v>8034645</v>
       </c>
       <c r="L612" s="5" t="n">
-        <v>16465</v>
+        <v>18642</v>
       </c>
       <c r="M612" s="3" t="inlineStr">
         <is>
@@ -40042,14 +40042,14 @@
       </c>
       <c r="J614" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K614" s="5" t="n">
-        <v>4737150</v>
+        <v>5363325</v>
       </c>
       <c r="L614" s="5" t="n">
-        <v>17610</v>
+        <v>19938</v>
       </c>
       <c r="M614" s="3" t="inlineStr">
         <is>
@@ -40608,14 +40608,14 @@
       </c>
       <c r="J623" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K623" s="5" t="n">
-        <v>4724100</v>
+        <v>5348550</v>
       </c>
       <c r="L623" s="5" t="n">
-        <v>17562</v>
+        <v>19883</v>
       </c>
       <c r="M623" s="3" t="inlineStr">
         <is>
@@ -41174,14 +41174,14 @@
       </c>
       <c r="J632" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K632" s="5" t="n">
-        <v>4709310</v>
+        <v>5331805</v>
       </c>
       <c r="L632" s="5" t="n">
-        <v>17507</v>
+        <v>19821</v>
       </c>
       <c r="M632" s="3" t="inlineStr">
         <is>
@@ -41740,14 +41740,14 @@
       </c>
       <c r="J641" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K641" s="5" t="n">
-        <v>4653630</v>
+        <v>5268765</v>
       </c>
       <c r="L641" s="5" t="n">
-        <v>17300</v>
+        <v>19586</v>
       </c>
       <c r="M641" s="3" t="inlineStr">
         <is>
@@ -43454,14 +43454,14 @@
       </c>
       <c r="J668" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K668" s="5" t="n">
-        <v>4612740</v>
+        <v>5222470</v>
       </c>
       <c r="L668" s="5" t="n">
-        <v>17148</v>
+        <v>19414</v>
       </c>
       <c r="M668" s="3" t="inlineStr">
         <is>
@@ -44586,14 +44586,14 @@
       </c>
       <c r="J686" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K686" s="5" t="n">
-        <v>4570110</v>
+        <v>5174205</v>
       </c>
       <c r="L686" s="5" t="n">
-        <v>16989</v>
+        <v>19235</v>
       </c>
       <c r="M686" s="3" t="inlineStr">
         <is>
@@ -45152,14 +45152,14 @@
       </c>
       <c r="J695" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K695" s="5" t="n">
-        <v>4557060</v>
+        <v>5159430</v>
       </c>
       <c r="L695" s="5" t="n">
-        <v>16941</v>
+        <v>19180</v>
       </c>
       <c r="M695" s="3" t="inlineStr">
         <is>
@@ -46866,14 +46866,14 @@
       </c>
       <c r="J722" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K722" s="5" t="n">
-        <v>4529220</v>
+        <v>5127910</v>
       </c>
       <c r="L722" s="5" t="n">
-        <v>16837</v>
+        <v>19063</v>
       </c>
       <c r="M722" s="3" t="inlineStr">
         <is>
@@ -47432,14 +47432,14 @@
       </c>
       <c r="J731" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K731" s="5" t="n">
-        <v>4503120</v>
+        <v>5098360</v>
       </c>
       <c r="L731" s="5" t="n">
-        <v>16740</v>
+        <v>18953</v>
       </c>
       <c r="M731" s="3" t="inlineStr">
         <is>
@@ -47874,14 +47874,14 @@
       </c>
       <c r="J738" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K738" s="5" t="n">
-        <v>6738150</v>
+        <v>7628825</v>
       </c>
       <c r="L738" s="5" t="n">
-        <v>15634</v>
+        <v>17700</v>
       </c>
       <c r="M738" s="3" t="inlineStr">
         <is>
@@ -47936,14 +47936,14 @@
       </c>
       <c r="J739" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K739" s="5" t="n">
-        <v>6800790</v>
+        <v>7699745</v>
       </c>
       <c r="L739" s="5" t="n">
-        <v>15816</v>
+        <v>17906</v>
       </c>
       <c r="M739" s="3" t="inlineStr">
         <is>
@@ -47998,14 +47998,14 @@
       </c>
       <c r="J740" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K740" s="5" t="n">
-        <v>4489200</v>
+        <v>5082600</v>
       </c>
       <c r="L740" s="5" t="n">
-        <v>16688</v>
+        <v>18894</v>
       </c>
       <c r="M740" s="3" t="inlineStr">
         <is>
@@ -48588,14 +48588,14 @@
       </c>
       <c r="J749" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K749" s="5" t="n">
-        <v>4476150</v>
+        <v>5067825</v>
       </c>
       <c r="L749" s="5" t="n">
-        <v>16640</v>
+        <v>18839</v>
       </c>
       <c r="M749" s="3" t="inlineStr">
         <is>
